--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -64,81 +64,93 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>08/09/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>sinh nhat</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>ốm</t>
+  </si>
+  <si>
     <t>02644075</t>
   </si>
   <si>
     <t>Huỳnh Đại Nhân</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t>18/09/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t>sinh nhat</t>
-  </si>
-  <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>無給休暇 / Nghỉ BHXH</t>
-  </si>
-  <si>
-    <t>ốm</t>
-  </si>
-  <si>
     <t>02222350</t>
   </si>
   <si>
@@ -167,18 +179,6 @@
   </si>
   <si>
     <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>08/09/2026</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
   </si>
   <si>
     <t>24/09/2026</t>
@@ -698,10 +698,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>17</v>
@@ -710,22 +710,22 @@
         <v>18</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>23</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -754,10 +754,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -798,22 +798,22 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>30</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -842,13 +842,13 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G7" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -886,22 +886,22 @@
         <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G8" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>30</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>23</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -930,19 +930,19 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G9" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>22</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
@@ -974,13 +974,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G10" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>20</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1018,19 +1018,19 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>50</v>
       </c>
       <c r="G11" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>22</v>
@@ -1062,19 +1062,19 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G12" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>22</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1106,7 +1106,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>54</v>

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -64,124 +64,124 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>sinh nhat</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>ốm</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
     <t>02020947</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t>08/09/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
     <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
-    <t>sinh nhat</t>
-  </si>
-  <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>無給休暇 / Nghỉ BHXH</t>
-  </si>
-  <si>
-    <t>ốm</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
-  </si>
-  <si>
-    <t>23/09/2026</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>24/09/2026</t>
   </si>
 </sst>
 </file>
@@ -669,39 +669,39 @@
         <v>19</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>17</v>
@@ -710,42 +710,42 @@
         <v>18</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -754,42 +754,42 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -798,42 +798,42 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -842,42 +842,42 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -886,42 +886,42 @@
         <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -930,42 +930,42 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
@@ -974,42 +974,42 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G10" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1018,42 +1018,42 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G11" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1071,33 +1071,33 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="8">
-        <v>2</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="J13" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -64,124 +64,139 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t>sinh nhat</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
     <t>02223526</t>
   </si>
   <si>
     <t>Nguyễn Thiên Phú</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>ốm</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kế hoạch nghỉ phép thay đổi </t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
   </si>
   <si>
     <t>23/09/2026</t>
   </si>
   <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>08/09/2026</t>
+  </si>
+  <si>
     <t>24/09/2026</t>
-  </si>
-  <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
-    <t>sinh nhat</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>無給休暇 / Nghỉ BHXH</t>
-  </si>
-  <si>
-    <t>ốm</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>08/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
   </si>
 </sst>
 </file>
@@ -669,28 +684,28 @@
         <v>19</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="8">
-        <v>2</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M3" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>26</v>
@@ -722,19 +737,19 @@
         <v>30</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>26</v>
@@ -742,10 +757,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -754,31 +769,31 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="J5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>26</v>
@@ -786,10 +801,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -798,31 +813,31 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G6" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M6" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>26</v>
@@ -830,10 +845,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -842,42 +857,42 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="J7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M7" s="7" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -886,31 +901,31 @@
         <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G8" s="8">
         <v>2</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="J8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M8" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>26</v>
@@ -918,10 +933,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -930,31 +945,31 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G9" s="8">
         <v>2</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="J9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M9" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>26</v>
@@ -962,10 +977,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
@@ -974,31 +989,31 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G10" s="8">
         <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="J10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M10" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>26</v>
@@ -1006,10 +1021,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1018,31 +1033,31 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G11" s="8">
         <v>0.5</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="J11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M11" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>26</v>
@@ -1050,10 +1065,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1062,31 +1077,31 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G12" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="L12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M12" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>26</v>
@@ -1094,10 +1109,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1106,51 +1121,79 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G13" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="J13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="L13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L13" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="M13" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="8"/>
+      <c r="A14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="8">
+        <v>2</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7"/>

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -64,40 +64,91 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>03/08/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>11/08/2026</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
     <t>02644066</t>
   </si>
   <si>
     <t>Nguyễn Hữu Tình</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t>16/09/2026</t>
   </si>
   <si>
     <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
   </si>
   <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
     <t>sinh nhat</t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>27/07/2026</t>
+  </si>
+  <si>
+    <t>29/07/2026</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>ốm</t>
   </si>
   <si>
     <t>02223526</t>
@@ -109,22 +160,25 @@
     <t>04/09/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>無給休暇 / Nghỉ BHXH</t>
-  </si>
-  <si>
-    <t>ốm</t>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kế hoạch nghỉ phép thay đổi </t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
   </si>
   <si>
     <t>02644075</t>
@@ -139,25 +193,25 @@
     <t>Buổi sáng/半日休暇 - 午前に</t>
   </si>
   <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>28/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kế hoạch nghỉ phép thay đổi </t>
-  </si>
-  <si>
-    <t>Từ chối</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
+    <t>19/08/2026</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>24/07/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
   </si>
   <si>
     <t>22/09/2026</t>
@@ -166,22 +220,10 @@
     <t>23/09/2026</t>
   </si>
   <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
+    <t>17/08/2026</t>
+  </si>
+  <si>
+    <t>06/08/2026</t>
   </si>
   <si>
     <t>02020947</t>
@@ -190,13 +232,31 @@
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
     <t>08/09/2026</t>
   </si>
   <si>
+    <t>08/07/2026</t>
+  </si>
+  <si>
+    <t>07/08/2026</t>
+  </si>
+  <si>
+    <t>sinh nhật</t>
+  </si>
+  <si>
     <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
+  </si>
+  <si>
+    <t>gia đình có việc gấp về quê</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
   </si>
 </sst>
 </file>
@@ -705,42 +765,42 @@
         <v>24</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="8">
         <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>23</v>
@@ -749,42 +809,42 @@
         <v>24</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>23</v>
@@ -793,43 +853,43 @@
         <v>24</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
       </c>
@@ -837,18 +897,18 @@
         <v>24</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -857,22 +917,22 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G7" s="8">
         <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>23</v>
@@ -881,18 +941,18 @@
         <v>24</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -901,22 +961,22 @@
         <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G8" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>23</v>
@@ -925,18 +985,18 @@
         <v>24</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -945,22 +1005,22 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G9" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>23</v>
@@ -968,19 +1028,17 @@
       <c r="L9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="M9" s="7"/>
       <c r="N9" s="8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
@@ -989,22 +1047,22 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G10" s="8">
         <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>23</v>
@@ -1013,18 +1071,18 @@
         <v>24</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1033,22 +1091,22 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="G11" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>23</v>
@@ -1057,18 +1115,18 @@
         <v>24</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1077,22 +1135,22 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="G12" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>23</v>
@@ -1101,18 +1159,18 @@
         <v>24</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1121,22 +1179,22 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>23</v>
@@ -1145,295 +1203,847 @@
         <v>24</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1">
+      <c r="A15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1">
+      <c r="A16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1">
+      <c r="A17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1">
+      <c r="A18" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="8">
+        <v>2</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1">
+      <c r="A19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1">
+      <c r="A20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="8">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1">
+      <c r="A21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1">
+      <c r="A22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1">
+      <c r="A23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1">
+      <c r="A24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1">
+      <c r="A25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1">
+      <c r="A26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="C26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="8">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1">
+      <c r="A27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="8">
+        <v>1</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1">
+      <c r="A28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="8">
+        <v>1</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1">
+      <c r="A29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="8">
         <v>2</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="8"/>
-    </row>
-    <row r="16" s="2" customFormat="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="8"/>
-    </row>
-    <row r="17" s="2" customFormat="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="8"/>
-    </row>
-    <row r="18" s="2" customFormat="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="8"/>
-    </row>
-    <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="8"/>
-    </row>
-    <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="8"/>
-    </row>
-    <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="8"/>
-    </row>
-    <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="8"/>
-    </row>
-    <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
-    </row>
-    <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="8"/>
-    </row>
-    <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="8"/>
-    </row>
-    <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="8"/>
-    </row>
-    <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="8"/>
+      <c r="H29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -12,7 +12,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet!$A$2:$F$6333</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -62,6 +62,39 @@
   </si>
   <si>
     <t>Trạng thái duyệt</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
   </si>
 </sst>
 </file>
@@ -533,20 +566,48 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="8"/>
+      <c r="A3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7"/>

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -94,7 +94,7 @@
     <t>Thân Trọng Tuấn</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
+    <t>Đã duyệt</t>
   </si>
 </sst>
 </file>

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -95,6 +95,27 @@
   </si>
   <si>
     <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
   </si>
 </sst>
 </file>
@@ -610,52 +631,136 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="8"/>
+      <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7"/>

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -64,58 +64,70 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
+  </si>
+  <si>
     <t>02121404</t>
   </si>
   <si>
     <t>Lê Hoàng Minh Tâm</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t>05/10/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>12/10/2026</t>
-  </si>
-  <si>
     <t>Buổi chiều/半日休暇 - 午後に</t>
   </si>
   <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t>09/10/2026</t>
-  </si>
-  <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
   </si>
 </sst>
 </file>
@@ -632,10 +644,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>17</v>
@@ -644,19 +656,19 @@
         <v>18</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G4" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>22</v>
@@ -676,10 +688,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -688,10 +700,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
@@ -720,10 +732,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -732,19 +744,19 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>22</v>
@@ -763,20 +775,48 @@
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7"/>

--- a/data/hrm_sync_leave_2.xlsx
+++ b/data/hrm_sync_leave_2.xlsx
@@ -64,37 +64,61 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
     <t>02020947</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t>09/10/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
   </si>
   <si>
     <t>02644057</t>
@@ -103,21 +127,6 @@
     <t>Phạm Văn Công</t>
   </si>
   <si>
-    <t>12/10/2026</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>05/10/2026</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
     <t>02223605</t>
   </si>
   <si>
@@ -127,7 +136,13 @@
     <t>14/10/2026</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
   </si>
 </sst>
 </file>
@@ -732,10 +747,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -744,10 +759,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G6" s="8">
         <v>0.5</v>
@@ -756,7 +771,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>22</v>
@@ -776,10 +791,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -788,19 +803,19 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G7" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>22</v>
@@ -815,40 +830,96 @@
         <v>22</v>
       </c>
       <c r="N7" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1">
+      <c r="A8" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="8"/>
+      <c r="B8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7"/>
